--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_348_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_348_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>7</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2707,16 +2707,16 @@
         <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -3491,10 +3491,10 @@
         <v>18</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>105</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>20</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4488,7 +4488,7 @@
         <v>-2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X37" t="n">
         <v>5</v>
@@ -4883,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X38" t="n">
         <v>6</v>
@@ -5272,16 +5272,16 @@
         <v>24</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -5468,7 +5468,7 @@
         <v>9</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6252,10 +6252,10 @@
         <v>15</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>91</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_348_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_348_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -692,20 +692,20 @@
         <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -854,17 +854,17 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2523,58 +2523,58 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -2719,14 +2719,14 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>3</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,58 +4892,58 @@
         <v>4</v>
       </c>
       <c r="X38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
         <v>6</v>
       </c>
-      <c r="Y38" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>7</v>
-      </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5284,10 +5284,10 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>11</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -6843,11 +6843,11 @@
         <v>11</v>
       </c>
       <c r="AK48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
